--- a/TESTS/zlit_5_charlie.xlsx
+++ b/TESTS/zlit_5_charlie.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,11 @@
           <t>Тип</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ГР</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -580,7 +585,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Роальд Дал — британський письменник відомий своїми дотепними і незвичними дитячими книгами</t>
+          <t>Роальд Дал</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -601,6 +606,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -622,7 +632,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Великобританія — Дал народився в Уельсі в родині норвезьких емігрантів</t>
+          <t>Великобританія</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -643,6 +653,11 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -687,6 +702,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -706,7 +726,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Він дуже бідний — жив з батьками і чотирма дідусями і бабусями у маленькій хаті і часто голодував</t>
+          <t>Він дуже бідний</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -727,6 +747,11 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -748,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Добрим скромним і вдячним — він цінує кожну дрібницю і любить родину</t>
+          <t>Добрим скромним і вдячним</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -769,6 +794,11 @@
       <c r="H6" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -790,7 +820,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Одну шоколадку — він їв її дуже повільно смакуючи кожен шматочок щоб насолода тривала довше</t>
+          <t>Одну шоколадку</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -811,6 +841,11 @@
       <c r="H7" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -832,7 +867,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>П'ять золотих квитків захованих у шоколадках Вонки — переможці отримали право відвідати фабрику</t>
+          <t>П'ять золотих квитків захованих у шоколадках Вонки</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -853,6 +888,11 @@
       <c r="H8" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -897,6 +937,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -916,7 +961,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Дідусь Джо — єдиний хто зміг встати з ліжка де лежали всі четверо дідусів і бабусь</t>
+          <t>Дідусь Джо</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -937,6 +982,11 @@
       <c r="H10" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -948,37 +998,42 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 1)</t>
+          <t>З ким живе Чарлі Бакет, крім батьків?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Сам із собакою</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>З чотирма дідусями й бабусями, що сплять у одній кімнаті</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>З тіткою і дядьком</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>З братами і сестрами</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -990,37 +1045,42 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 2)</t>
+          <t>Чим харчується родина Бакетів зазвичай?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Дорогими стравами</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Дуже скромно — переважно капустяним супом, особливо коли грошей зовсім мало</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Лише шоколадом</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Фастфудом</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1032,37 +1092,42 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 3)</t>
+          <t>Хто з родини найбільше розповідає Чарлі про містера Вонку та його фабрику?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Мама</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Дідусь Джо, що колись там працював</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Тато</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Сусід</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1074,37 +1139,42 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 1)</t>
+          <t>Хто першим у книзі знайшов золотий квиток?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Чарлі</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Август Глуп — хлопчик, що постійно їсть</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Верука Солт</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Віолетта Борегард</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1116,37 +1186,42 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 2)</t>
+          <t>Чим прославилась Верука Солт, перш ніж знайти золотий квиток?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Спортивними досягненнями</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Тим, що батьки купували їй усе, що вона забажає</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Добрими вчинками</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Талантом до малювання</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1158,37 +1233,42 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 3)</t>
+          <t>Чим займалась Віолетта Борегард, коли отримала свій золотий квиток?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Грою на піаніно</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Жуванням однієї й тієї самої жувальної гумки рекордно довго</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Читанням книг</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Малюванням</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1200,37 +1280,42 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 1)</t>
+          <t>Чим був одержимий хлопчик Майк Тіві?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Спортом</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Перегляданням телевізора, особливо фільмів зі стріляниною</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Музикою</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Тваринами</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1242,37 +1327,42 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 2)</t>
+          <t>Коли діти з золотими квитками мали з'явитися біля фабрики Вонки?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Через місяць</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Першого числа наступного місяця, рівно в десяту годину</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Через тиждень</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>У день народження Вонки</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1284,37 +1374,42 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 3)</t>
+          <t>Хто супроводжував кожну дитину на екскурсію по фабриці?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Усі члени родини</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Лише по одному з батьків/родичів на кожну дитину</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Учителі</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Ніхто, лише діти</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1326,37 +1421,42 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 1)</t>
+          <t>Як виглядав Віллі Вонка, коли вперше зустрів дітей біля брами фабрики?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Сумним і втомленим</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Ексцентричним, у яскравому костюмі та циліндрі, з гострою бородою</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Звичайним робітником</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>У робочому халаті без прикрас</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1368,37 +1468,42 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 2)</t>
+          <t>Що дивовижне побачили діти, щойно зайшовши у перший цех фабрики?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Звичайні машини</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Шоколадну річку та водоспад, з якого збивали шоколад</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Порожню залу</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Велику бібліотеку</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1410,37 +1515,42 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 3)</t>
+          <t>Хто такі Умпа-Лумпи, яких діти зустріли на фабриці?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Роботи</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Маленькі працівники фабрики, що співають піснями про неслухняних дітей</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Тварини</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Привиди</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1452,37 +1562,42 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 1)</t>
+          <t>Чому Август Глуп впав у шоколадну річку?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Його штовхнули</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Він не послухав попередження і нахилився, щоб пити шоколад прямо з річки</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він послизнувся випадково</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Йому стало погано</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1494,37 +1609,42 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 2)</t>
+          <t>Куди потрапив Август Глуп після падіння в річку?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Залишився плавати</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Його затягло у трубу, що веде до цеху виготовлення помадки</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він виплив сам</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Його витягли одразу</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1536,37 +1656,42 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 3)</t>
+          <t>Як Умпа-Лумпи відреагували на пригоду з Августом?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Засмутились мовчки</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Заспівали пісню про те, що жадібність до добра не доводить</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Покликали лікаря мовчки</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Заплакали</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1578,37 +1703,42 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 1)</t>
+          <t>Чого зажадала Верука Солт у кімнаті, де білки лущили горіхи?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Шоколадку</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Білку, яка лущить горіхи, негайно і саме зараз</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Цукерку</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Іграшку</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1620,37 +1750,42 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 2)</t>
+          <t>Що сталося з Верукою, коли вона спробувала схопити білку?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Білка втекла</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Білки визнали її «гнилим горіхом» і кинули в сміттєпровід</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Її покарали батьки</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Нічого не сталося</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1662,37 +1797,42 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 3)</t>
+          <t>Як батьки Веруки повели себе після цієї пригоди?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Спокійно пішли геть</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Кинулись за нею в сміттєпровід і теж зникли з туру</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Посварились із Вонкою</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Розсміялись</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1704,37 +1844,42 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 1)</t>
+          <t>Що сталося з Віолеттою після того, як вона спробувала експериментальну жувальну гумку-обід?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Нічого</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вона перетворилася на велику чорницю, і її довелося відтискати</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вона заснула</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вона зникла</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1746,37 +1891,42 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 2)</t>
+          <t>Що сталося з Майком Тіві у кімнаті телепортації по телевізору?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він виграв приз</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Його зменшило до кількох сантиметрів через телепортацію</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він заснув</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Нічого не сталося</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1788,37 +1938,42 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 3)</t>
+          <t>Хто з дітей залишився єдиним «непошкодженим» наприкінці екскурсії?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Август Глуп</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Чарлі Бакет</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Верука Солт</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Майк Тіві</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1843,8 +1998,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>А</t>
@@ -1853,6 +2006,11 @@
       <c r="H32" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1877,8 +2035,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>Б</t>
@@ -1887,6 +2043,11 @@
       <c r="H33" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1911,8 +2072,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>А</t>
@@ -1921,6 +2080,11 @@
       <c r="H34" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1932,21 +2096,19 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Що символізують чотири «порочні» дитини у книзі?</t>
+          <t>Кожна з чотирьох неслухняних дітей у книзі уособлює певний порок, за який її «карає» фабрика.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>А</t>
@@ -1955,6 +2117,11 @@
       <c r="H35" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1966,29 +2133,32 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Яка риса стилю Роальда Дала помітна у «Чарлі і шоколадній фабриці»?</t>
+          <t>У творах Роальда Дала покарання неслухняних дітей описані м'яко, без жодного гумору чи перебільшення.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2000,21 +2170,19 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Яку роль відіграють Умпа-Лумпи на фабриці?</t>
+          <t>Умпа-Лумпи на фабриці виконують усю роботу і коментують події піснями.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>А</t>
@@ -2023,6 +2191,11 @@
       <c r="H37" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2034,21 +2207,19 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Що сталося з Вайолет Борегард?</t>
+          <t>Після пригоди в кімнаті з білками Веруку Солт визнали «гнилим горіхом».</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>А</t>
@@ -2057,6 +2228,11 @@
       <c r="H38" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2068,29 +2244,32 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Чим завершилась подорож фабрикою для Чарлі?</t>
+          <t>Подорож фабрикою завершилась тим, що Вонка подарував фабрику Августу Глупу як найслухнянішому.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2102,21 +2281,19 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Яка головна ідея книги «Чарлі і шоколадна фабрика»?</t>
+          <t>Головна ідея книги — скромність, доброта і чесність винагороджуються, а пороки караються.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
           <t>А</t>
@@ -2125,6 +2302,11 @@
       <c r="H40" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2169,6 +2351,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2211,6 +2398,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2220,27 +2412,27 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Які пороки уособлюють діти-переможці крім Чарлі?</t>
+          <t>Що сталося з кожною з чотирьох неслухняних дітей на фабриці?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Жадібність (Август Глуп)</t>
+          <t>Августа Глупа затягло у трубу для помадки</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Пиха (Верука Солт)</t>
+          <t>Веруку Солт викинули як «гнилий горіх»</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Доброта (Майк Тіві)</t>
+          <t>Усі четверо отримали головний приз</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ледарство (Майк Тіві, грубість)</t>
+          <t>Майка Тіві зменшила телепортація</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2251,6 +2443,11 @@
       <c r="H43" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2469,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Дивакуватий геніальний і трохи загадковий творець шоколаду — він заховав свою фабрику від усіх</t>
+          <t>Дивакуватий геніальний і трохи загадковий творець шоколаду</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2293,6 +2490,11 @@
       <c r="H44" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2516,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Кожен уособлював якийсь порок: жадібність пихатість ледарство грубість — і кожен поплатився за свій порок</t>
+          <t>Кожен уособлював якийсь порок: жадібність пихатість ледарство грубість</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2335,6 +2537,11 @@
       <c r="H45" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2563,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Жадібний хлопчик впав у шоколадну річку і потрапив у трубу — його жадібність його занапастила</t>
+          <t>Жадібний хлопчик впав у шоколадну річку і потрапив у трубу</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2377,6 +2584,11 @@
       <c r="H46" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
